--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3468,9 +3468,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A07D1E-B61B-45E9-AE56-9D44B63E7A12}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228BF7B3-B66B-4F31-846B-AD07D682FA0F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A862BF9D-18DC-4B9D-80A0-2914F9A4DD00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FF24A93-1927-4C8A-A0FF-12662422A899}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -843,6 +843,9 @@
           <t>Camelus</t>
         </is>
       </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
       <c r="E15">
         <v>570</v>
       </c>
@@ -1620,7 +1623,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TRUEX and CARPENTER, 1969</t>
+          <t>LASSEK, 1942</t>
         </is>
       </c>
       <c r="H33">
@@ -2433,6 +2436,9 @@
           <t>Manis pentadactyla</t>
         </is>
       </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
       <c r="E52">
         <v>18</v>
       </c>
@@ -2641,7 +2647,7 @@
         <v>3</v>
       </c>
       <c r="E57">
-        <v>0.12</v>
+        <v>12</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -2742,6 +2748,9 @@
       <c r="D59">
         <v>2</v>
       </c>
+      <c r="E59">
+        <v>17</v>
+      </c>
       <c r="H59">
         <v>9</v>
       </c>
@@ -2853,7 +2862,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -3204,8 +3213,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -3467,10 +3476,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228BF7B3-B66B-4F31-846B-AD07D682FA0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{768C9075-8203-4414-881B-B0611811257C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FF24A93-1927-4C8A-A0FF-12662422A899}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48624FF7-08B7-493A-9EC1-347E49C52E5A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAA7EB52-F3F2-47E8-A20A-B9381BCF936B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{768C9075-8203-4414-881B-B0611811257C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E9177D-0531-4B81-9389-C05EA6C65781}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48624FF7-08B7-493A-9EC1-347E49C52E5A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D67F814-1763-4652-BBC5-96C1F639883B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAA7EB52-F3F2-47E8-A20A-B9381BCF936B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAEFFCE1-BD0B-4180-9B28-CB20A843B7B5}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E9177D-0531-4B81-9389-C05EA6C65781}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D39C966D-7157-48D4-A833-0DA09723A7CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D67F814-1763-4652-BBC5-96C1F639883B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198370CD-F0B3-412A-89B7-8B980E579943}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAEFFCE1-BD0B-4180-9B28-CB20A843B7B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3369192-D4E0-463B-8DDC-4DFAFF8857F0}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D39C966D-7157-48D4-A833-0DA09723A7CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A327878C-C077-49BE-97FA-DDB540E52037}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198370CD-F0B3-412A-89B7-8B980E579943}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A547A5C-E024-4A73-B9DF-54AE50068D81}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3369192-D4E0-463B-8DDC-4DFAFF8857F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EEBDFC-DB21-417E-8577-BE6143DB4F81}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A327878C-C077-49BE-97FA-DDB540E52037}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A4D31DF-1D6B-4BD9-A769-E973C19BBA91}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A547A5C-E024-4A73-B9DF-54AE50068D81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCA48C8E-0A4C-4CFD-AF38-1A01555C15EA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EEBDFC-DB21-417E-8577-BE6143DB4F81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0AC0C5F-A7B6-41BC-947B-1A67F80B48C8}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A4D31DF-1D6B-4BD9-A769-E973C19BBA91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EE9BC15-02B0-450E-9EAB-1B55D02C065C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCA48C8E-0A4C-4CFD-AF38-1A01555C15EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7E5DA11-416B-4875-ACC2-3E3809D7940C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0AC0C5F-A7B6-41BC-947B-1A67F80B48C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F2435CC-6036-45CB-8EF0-5D2BC41B4C76}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EE9BC15-02B0-450E-9EAB-1B55D02C065C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89E6B889-3AA9-4C9B-851E-1F0CFAA625ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7E5DA11-416B-4875-ACC2-3E3809D7940C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{960284E3-2E9A-4788-BFFB-50CE5A6F89C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F2435CC-6036-45CB-8EF0-5D2BC41B4C76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779F1917-AD60-4FC0-A106-C8FBF43F6958}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89E6B889-3AA9-4C9B-851E-1F0CFAA625ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29428637-7A3C-4DC9-8103-7E18CBE9B104}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{960284E3-2E9A-4788-BFFB-50CE5A6F89C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627172B8-4016-4481-B572-9C720C696716}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779F1917-AD60-4FC0-A106-C8FBF43F6958}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{432A4CE3-3500-4DC4-9FAD-294F1B0E7964}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29428637-7A3C-4DC9-8103-7E18CBE9B104}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{881EC9D8-F690-4ECC-8AB1-B87AE6595F47}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627172B8-4016-4481-B572-9C720C696716}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B7839FB-537E-41EE-A56E-0CBE9A708F74}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{432A4CE3-3500-4DC4-9FAD-294F1B0E7964}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{584D639C-B496-49B2-B854-C1F3E094B94E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{881EC9D8-F690-4ECC-8AB1-B87AE6595F47}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2050B4FB-58CB-4C44-B0C6-68AA32185064}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B7839FB-537E-41EE-A56E-0CBE9A708F74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE997D6E-0E37-4687-B267-0A4D1A27E77E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{584D639C-B496-49B2-B854-C1F3E094B94E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067FFF11-C272-4791-967A-96A1E1AB606E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2050B4FB-58CB-4C44-B0C6-68AA32185064}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEDF3961-9330-49A4-9F9A-CF95DF37DFA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE997D6E-0E37-4687-B267-0A4D1A27E77E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4202145-4A01-47FC-A051-09591FC6D611}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067FFF11-C272-4791-967A-96A1E1AB606E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3850E62-C2E5-445B-8CD4-892C9E46B0D4}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEDF3961-9330-49A4-9F9A-CF95DF37DFA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD2C9E8A-6A06-4FED-9C45-76CF5EF40CAD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4202145-4A01-47FC-A051-09591FC6D611}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AEB9AC8-F565-4E79-9308-81C1C9DB0659}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3850E62-C2E5-445B-8CD4-892C9E46B0D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81611AFB-F0A4-4448-84D1-CE4812F3EA71}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3488,13 +3488,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD2C9E8A-6A06-4FED-9C45-76CF5EF40CAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA347322-1114-46EB-A864-8459E9E73C9E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AEB9AC8-F565-4E79-9308-81C1C9DB0659}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF181F5B-F7BF-426F-A746-5C764CC0D6B0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81611AFB-F0A4-4448-84D1-CE4812F3EA71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{192B76C3-FD29-41AB-ACBA-ED782030CC31}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,75 +372,85 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Species_as_printed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>species_basis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Digital dexterity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Body weight kg</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Number of fibers per tract</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Number of fibers per tract ref</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Largest fiber diameter µm</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Largest fiber diameter µm ref</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Average fiber size x 10ˆ5 K</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Area of tract mmˆ2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Area of tract mmˆ2 ref</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Penetration down spinal cord</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Penetration down spinal cord ref</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lamina of axon terminals deepest</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lamina of axon terminals deepest ref</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Lamina of axon terminals densest</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Lamina of axon terminals densest ref</t>
         </is>
@@ -457,21 +467,31 @@
           <t>Orycteropus afer</t>
         </is>
       </c>
-      <c r="D2">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Orycteropus afer</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F2">
         <v>2</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>60</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>0.53</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Upper C</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
@@ -488,21 +508,31 @@
           <t>Myrmecophaga jubata</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Myrmecophaga jubata</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>20</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>10</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>0.6</v>
       </c>
     </row>
@@ -522,42 +552,52 @@
           <t>Dasypus novemcinctus</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dasypus novemcinctus</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>5</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>2</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>0.6</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>FISHER el al., 1969</t>
         </is>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>8</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>FISHER el al., 1969</t>
         </is>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>6</v>
       </c>
     </row>
@@ -572,13 +612,23 @@
           <t>Desmodus rufus</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Desmodus rufus</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>0.033</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>0.01</v>
       </c>
     </row>
@@ -593,13 +643,23 @@
           <t>Horpyiocepalus leucogostra</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Horpyiocepalus leucogostra</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>0.01</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>0.04</v>
       </c>
     </row>
@@ -614,21 +674,31 @@
           <t>Myotis</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Myotis</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>0.03</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>0.01</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>BROERE, 1966</t>
         </is>
@@ -645,13 +715,23 @@
           <t>Pteropus edulis</t>
         </is>
       </c>
-      <c r="D8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pteropus edulis</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>0.9</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>0.12</v>
       </c>
     </row>
@@ -666,13 +746,23 @@
           <t>Rhinolophus</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rhinolophus</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>0.016</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>0.01</v>
       </c>
     </row>
@@ -684,22 +774,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Tadarida cynocephala</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Tasarida cynocephala</t>
         </is>
       </c>
-      <c r="D10">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>1.3</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>8000</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>0.25</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>0.02</v>
       </c>
     </row>
@@ -709,13 +809,18 @@
           <t>Bear (assume Brown)</t>
         </is>
       </c>
-      <c r="D11">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unspecified_in_source</t>
+        </is>
+      </c>
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>200</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>9.210000000000001</v>
       </c>
     </row>
@@ -727,21 +832,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Castor canadensis</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Castor canadiensis</t>
         </is>
       </c>
-      <c r="D12">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F12">
         <v>3</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>13</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>DOUGLAS and BARR, 1950</t>
         </is>
@@ -763,34 +878,44 @@
           <t>Galago crassicaudatus</t>
         </is>
       </c>
-      <c r="D13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Galago crassicaudatus</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F13">
         <v>5</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>1.14</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>FERRER, 1971</t>
         </is>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>9</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>FERRER, 1971</t>
         </is>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>6</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>FERRER, 1971</t>
         </is>
@@ -807,26 +932,36 @@
           <t>Galago senegalensis</t>
         </is>
       </c>
-      <c r="D14">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Galago senegalensis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F14">
         <v>5</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>0.26</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>2.5</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Lower L</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
@@ -843,16 +978,26 @@
           <t>Camelus</t>
         </is>
       </c>
-      <c r="D15">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Camelus</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F15">
         <v>1</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>570</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>6</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
@@ -874,56 +1019,66 @@
           <t>Felis catus</t>
         </is>
       </c>
-      <c r="D16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Felis catus</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>3.5</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>186000</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>5</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>SCHIEBEL and SCHIEBEL, 1966</t>
         </is>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>0.6</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>1.13</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>NYBERG-HANSEN and BRODAL, 1963</t>
         </is>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>8</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>NYBERG-HANSEN and BRODAL, 1963</t>
         </is>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>6</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>NYBERG-HANSEN and BRODAL, 1963</t>
         </is>
@@ -945,48 +1100,58 @@
           <t>Pan troglodytes</t>
         </is>
       </c>
-      <c r="D17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pan troglodytes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F17">
         <v>6</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>44</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>807000</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>LASSEK and WHEATLEY, 1945</t>
         </is>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>0.96</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>7.77</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>coccygeal</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>10</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>6</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -1003,21 +1168,31 @@
           <t>Tamias striatus</t>
         </is>
       </c>
-      <c r="D18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tamias striatus</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F18">
         <v>3</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>0.1</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>0.26</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>SIMPSON, 1914</t>
         </is>
@@ -1029,40 +1204,45 @@
           <t>Cow (unspecified)</t>
         </is>
       </c>
-      <c r="D19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>unspecified_in_source</t>
+        </is>
+      </c>
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>500</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>540000</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>5</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>0.55</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>2.97</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Upper C</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
@@ -1079,37 +1259,47 @@
           <t>Myocastor coypus</t>
         </is>
       </c>
-      <c r="D20">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Myocastor coypus</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F20">
         <v>3</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>5</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>8</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>GOLDBY and KACKER, 1963</t>
         </is>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>0.37</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>GOLDBY and KACKER, 1963</t>
         </is>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>6</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>GOLDBY and KACKER, 1963</t>
         </is>
@@ -1121,40 +1311,45 @@
           <t>Deer (unspecified)</t>
         </is>
       </c>
-      <c r="D21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>unspecified_in_source</t>
+        </is>
+      </c>
+      <c r="F21">
         <v>1</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>200</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>490000</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>6</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>0.58</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>2.89</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Upper C</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
@@ -1176,40 +1371,50 @@
           <t>Canis familiaris</t>
         </is>
       </c>
-      <c r="D22">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Canis familiaris</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>11</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>285500</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>1.22</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>3.49</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>BUXTON and GOODMAN, 1967</t>
         </is>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>8</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>BUXTON and GOODMAN, 1967</t>
         </is>
@@ -1223,32 +1428,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Elephas maximus</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Elephus maximus</t>
         </is>
       </c>
-      <c r="D23">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F23">
         <v>1</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>6000</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>8</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>VERHAART, 1963</t>
         </is>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>5.13</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Middle T</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>VERHAART, 1963</t>
         </is>
@@ -1270,29 +1485,39 @@
           <t>Putorius furo</t>
         </is>
       </c>
-      <c r="D24">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Putorius furo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F24">
         <v>3</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>0.9</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>90000</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>NOORDUYN, 1959</t>
         </is>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>10</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>NOORDUYN, 1959</t>
         </is>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>1.5</v>
       </c>
     </row>
@@ -1307,56 +1532,66 @@
           <t>Hylobates lar</t>
         </is>
       </c>
-      <c r="D25">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Hylobates lar</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F25">
         <v>6</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>6</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>315000</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>VERHAART, 1948b</t>
         </is>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>12</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>1.09</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <v>3.44</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="O25">
+      <c r="Q25">
         <v>10</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="Q25">
+      <c r="S25">
         <v>6</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -1373,24 +1608,34 @@
           <t>Hylobates syndactylus</t>
         </is>
       </c>
-      <c r="D26">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Hylobates syndactylus</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F26">
         <v>6</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>10</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>239700</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>VERHAART, 1948b</t>
         </is>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>1.35</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>3.25</v>
       </c>
     </row>
@@ -1405,48 +1650,58 @@
           <t>Capra hircus</t>
         </is>
       </c>
-      <c r="D27">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Capra hircus</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F27">
         <v>1</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>80</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>260000</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>5</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>0.21</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>0.569</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>HAARTSEN and VERHAART, 1967</t>
         </is>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>6</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>HAARTSEN and VERHAART, 1967</t>
         </is>
@@ -1460,21 +1715,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Spermophilus tridecemlineatus</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Spermophillus tridecemlineatus</t>
         </is>
       </c>
-      <c r="D28">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F28">
         <v>3</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>0.65</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>SIMPSON,1915</t>
         </is>
@@ -1491,13 +1756,23 @@
           <t>Cavia aperea</t>
         </is>
       </c>
-      <c r="D29">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cavia aperea</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F29">
         <v>2</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>0.6</v>
       </c>
-      <c r="K29">
+      <c r="M29">
         <v>0.33</v>
       </c>
     </row>
@@ -1512,26 +1787,36 @@
           <t>Cricetus auratus</t>
         </is>
       </c>
-      <c r="D30">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cricetus auratus</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F30">
         <v>3</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>0.5</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>480000</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>DOUGLAS and BARR, 1950</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>DOUGLAS and BARR, 1950</t>
         </is>
@@ -1545,24 +1830,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Erinaceus</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Erinaceous</t>
         </is>
       </c>
-      <c r="D31">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F31">
         <v>2</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>0.75</v>
       </c>
-      <c r="K31">
+      <c r="M31">
         <v>0.02</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Upper C</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
@@ -1579,18 +1874,28 @@
           <t>Paraechinus</t>
         </is>
       </c>
-      <c r="D32">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Paraechinus</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F32">
         <v>2</v>
       </c>
-      <c r="E32">
+      <c r="G32">
         <v>0.5</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Upper C</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>ROBARDS, personal commun.; CAMPBELL, 1967</t>
         </is>
@@ -1612,32 +1917,42 @@
           <t>Sus scrofa</t>
         </is>
       </c>
-      <c r="D33">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sus scrofa</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F33">
         <v>1</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>90</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>210000</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>5</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>0.85</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <v>1.8</v>
       </c>
     </row>
@@ -1652,21 +1967,31 @@
           <t>Equus caballus</t>
         </is>
       </c>
-      <c r="D34">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Equus caballus</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F34">
         <v>1</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>350</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>5</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>2.68</v>
       </c>
     </row>
@@ -1681,26 +2006,36 @@
           <t>Potos flavus</t>
         </is>
       </c>
-      <c r="D35">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Potos flavus</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F35">
         <v>3</v>
       </c>
-      <c r="E35">
+      <c r="G35">
         <v>2.1</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Lower L</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>HARTING and NOBACK, 1970</t>
         </is>
       </c>
-      <c r="O35">
+      <c r="Q35">
         <v>10</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>HARTING and NOBACK, 1970</t>
         </is>
@@ -1717,26 +2052,36 @@
           <t>Lemur catta</t>
         </is>
       </c>
-      <c r="D36">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lemur catta</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F36">
         <v>5</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>2.1</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>3</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Lower L</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
@@ -1758,40 +2103,50 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D37">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F37">
         <v>7</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>70</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>1101000</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>22</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>TRUEX and CARPENTER, 1969</t>
         </is>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>1.03</v>
       </c>
-      <c r="K37">
+      <c r="M37">
         <v>11.43</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>coccygeal</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>TRUEX and CARPENTER, 1969</t>
         </is>
@@ -1808,29 +2163,39 @@
           <t>Scalopus aquaticus</t>
         </is>
       </c>
-      <c r="D38">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Scalopus aquaticus</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F38">
         <v>1</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>0.1</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>4</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>BISHOP et al., 1971</t>
         </is>
       </c>
-      <c r="K38">
+      <c r="M38">
         <v>0.01</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Upper T</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>LINOWIECKI, 1914</t>
         </is>
@@ -1844,59 +2209,69 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Ateles ater</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Ateleus ater</t>
         </is>
       </c>
-      <c r="D39">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Iwaniuk_etal_1999</t>
+        </is>
+      </c>
+      <c r="F39">
         <v>4</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <v>6</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>505000</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>LASSEK, 1943</t>
         </is>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>12</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>LASSEK, 1943</t>
         </is>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>0.63</v>
       </c>
-      <c r="K39">
+      <c r="M39">
         <v>3.23</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>coccygeal</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="O39">
+      <c r="Q39">
         <v>10</v>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>PETRAS, 1969</t>
         </is>
       </c>
-      <c r="Q39">
+      <c r="S39">
         <v>6</v>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -1918,37 +2293,47 @@
           <t>Cebus apella</t>
         </is>
       </c>
-      <c r="D40">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cebus apella</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F40">
         <v>5</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>1.25</v>
       </c>
-      <c r="K40">
+      <c r="M40">
         <v>2</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>coccygeal</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="O40">
+      <c r="Q40">
         <v>10</v>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>PETRAS, 1969</t>
         </is>
       </c>
-      <c r="Q40">
+      <c r="S40">
         <v>6</v>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -1970,34 +2355,44 @@
           <t>Cercopithecus pygerythrus</t>
         </is>
       </c>
-      <c r="D41">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cercopithecus pygerythrus</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F41">
         <v>6</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <v>4</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>coccygeal</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="O41">
+      <c r="Q41">
         <v>10</v>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>PETRAS, 1969</t>
         </is>
       </c>
-      <c r="Q41">
+      <c r="S41">
         <v>6</v>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -2014,45 +2409,50 @@
           <t>Lagothrix lagotricha</t>
         </is>
       </c>
-      <c r="D42">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lagothrix lagotricha</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F42">
         <v>5</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>6</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>coccygeal</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="O42">
+      <c r="Q42">
         <v>10</v>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="Q42">
+      <c r="S42">
         <v>6</v>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
-      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Monkey (macaque)</t>
@@ -2060,27 +2460,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Macaca irus</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Macaca ira</t>
         </is>
       </c>
-      <c r="D43">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F43">
         <v>6</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>5</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>195000</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>VERHAART, 1948a</t>
         </is>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>0.6</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <v>1.18</v>
       </c>
     </row>
@@ -2100,48 +2510,58 @@
           <t>Macaca mulatta</t>
         </is>
       </c>
-      <c r="D44">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Macaca mulatta</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F44">
         <v>6</v>
       </c>
-      <c r="E44">
+      <c r="G44">
         <v>8.300000000000001</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>400000</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>DEMEYER and RUSSEL, 1958</t>
         </is>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>0.72</v>
       </c>
-      <c r="K44">
+      <c r="M44">
         <v>2.89</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>coccygeal</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="O44">
+      <c r="Q44">
         <v>10</v>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>PETRAS, 1969</t>
         </is>
       </c>
-      <c r="Q44">
+      <c r="S44">
         <v>6</v>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -2163,16 +2583,26 @@
           <t>Papio papio</t>
         </is>
       </c>
-      <c r="D45">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Papio papio</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F45">
         <v>6</v>
       </c>
-      <c r="E45">
+      <c r="G45">
         <v>25</v>
       </c>
-      <c r="O45">
+      <c r="Q45">
         <v>10</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>PHILLIPS, 1967</t>
         </is>
@@ -2186,29 +2616,39 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Saguinus oedipus</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>Saquinas oedipus</t>
         </is>
       </c>
-      <c r="D46">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Iwaniuk_etal_1999</t>
+        </is>
+      </c>
+      <c r="F46">
         <v>4</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <v>0.4</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>SHRIVER and MATZKE, 1965</t>
         </is>
       </c>
-      <c r="O46">
+      <c r="Q46">
         <v>6</v>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>SHRIVER and MATZKE, 1965</t>
         </is>
@@ -2230,45 +2670,55 @@
           <t>Saimiri sciureus</t>
         </is>
       </c>
-      <c r="D47">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Saimiri sciureus</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F47">
         <v>5</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>0.75</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>8</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K47">
+      <c r="M47">
         <v>0.7</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
       </c>
-      <c r="O47">
+      <c r="Q47">
         <v>9</v>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>HARTING AND NOBACK, 1970</t>
         </is>
       </c>
-      <c r="Q47">
+      <c r="S47">
         <v>6</v>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>HARTING AND NOBACK, 1970</t>
         </is>
@@ -2285,24 +2735,29 @@
           <t>Mouse (unspecified)</t>
         </is>
       </c>
-      <c r="D48">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>unspecified_in_source</t>
+        </is>
+      </c>
+      <c r="F48">
         <v>3</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>0.025</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>32300</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
-      <c r="J48">
+      <c r="L48">
         <v>0.21</v>
       </c>
-      <c r="K48">
+      <c r="M48">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -2317,32 +2772,42 @@
           <t>Equus</t>
         </is>
       </c>
-      <c r="D49">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Equus</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F49">
         <v>1</v>
       </c>
-      <c r="E49">
+      <c r="G49">
         <v>250</v>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>412000</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="H49">
+      <c r="J49">
         <v>5</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="J49">
+      <c r="L49">
         <v>0.9</v>
       </c>
-      <c r="K49">
+      <c r="M49">
         <v>3.74</v>
       </c>
     </row>
@@ -2354,51 +2819,61 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Didelphis virginiana</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Didelphis</t>
         </is>
       </c>
-      <c r="D50">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Iwaniuk_etal_1999_imputed</t>
+        </is>
+      </c>
+      <c r="F50">
         <v>3</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <v>3.7</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>48100</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>TOWE, 1973</t>
         </is>
       </c>
-      <c r="J50">
+      <c r="L50">
         <v>0.45</v>
       </c>
-      <c r="K50">
+      <c r="M50">
         <v>0.22</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Upper T</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>BAUTISTA and MATZKE, 1965</t>
         </is>
       </c>
-      <c r="O50">
+      <c r="Q50">
         <v>8</v>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>MARTIN and FISHER, 1968</t>
         </is>
       </c>
-      <c r="Q50">
+      <c r="S50">
         <v>5</v>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>MARTIN and FISHER, 1968</t>
         </is>
@@ -2415,13 +2890,23 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D51">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pongo pygmaeus</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F51">
         <v>6</v>
       </c>
-      <c r="E51">
+      <c r="G51">
         <v>60</v>
       </c>
-      <c r="K51">
+      <c r="M51">
         <v>2.61</v>
       </c>
     </row>
@@ -2436,21 +2921,31 @@
           <t>Manis pentadactyla</t>
         </is>
       </c>
-      <c r="D52">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Manis pentadactyla</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F52">
         <v>1</v>
       </c>
-      <c r="E52">
+      <c r="G52">
         <v>18</v>
       </c>
-      <c r="H52">
+      <c r="J52">
         <v>2.5</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K52">
+      <c r="M52">
         <v>0.16</v>
       </c>
     </row>
@@ -2465,37 +2960,47 @@
           <t>Trichosurus vulpecula</t>
         </is>
       </c>
-      <c r="D53">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Trichosurus vulpecula</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F53">
         <v>3</v>
       </c>
-      <c r="E53">
+      <c r="G53">
         <v>3.5</v>
       </c>
-      <c r="K53">
+      <c r="M53">
         <v>0.54</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Lower T</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>REES and HORE, 1970; MARTIN et al., 1970</t>
         </is>
       </c>
-      <c r="O53">
+      <c r="Q53">
         <v>8</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>REES and HORE, 1970; MARTIN et al., 1970</t>
         </is>
       </c>
-      <c r="Q53">
+      <c r="S53">
         <v>6</v>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>REES and HORE, 1970; MARTIN et al., 1970</t>
         </is>
@@ -2512,21 +3017,31 @@
           <t>Microsorex hoyi</t>
         </is>
       </c>
-      <c r="D54">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Microsorex hoyi</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F54">
         <v>2</v>
       </c>
-      <c r="E54">
+      <c r="G54">
         <v>0.003</v>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>1</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K54">
+      <c r="M54">
         <v>0.02</v>
       </c>
     </row>
@@ -2541,37 +3056,47 @@
           <t>Setonix brachyurus</t>
         </is>
       </c>
-      <c r="D55">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Setonix brachyurus</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F55">
         <v>3</v>
       </c>
-      <c r="E55">
+      <c r="G55">
         <v>3.5</v>
       </c>
-      <c r="K55">
+      <c r="M55">
         <v>0.1</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>WATSON, 1971</t>
         </is>
       </c>
-      <c r="O55">
+      <c r="Q55">
         <v>6</v>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>WATSON, 1971</t>
         </is>
       </c>
-      <c r="Q55">
+      <c r="S55">
         <v>5</v>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>WATSON, 1971</t>
         </is>
@@ -2593,40 +3118,50 @@
           <t>Oryctolagus cuniculus</t>
         </is>
       </c>
-      <c r="D56">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Oryctolagus cuniculus</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F56">
         <v>2</v>
       </c>
-      <c r="E56">
+      <c r="G56">
         <v>1.8</v>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>101700</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
-      <c r="H56">
+      <c r="J56">
         <v>4</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="J56">
+      <c r="L56">
         <v>0.27</v>
       </c>
-      <c r="K56">
+      <c r="M56">
         <v>0.28</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
@@ -2643,26 +3178,36 @@
           <t>Procyon lotor</t>
         </is>
       </c>
-      <c r="D57">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Procyon lotor</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F57">
         <v>3</v>
       </c>
-      <c r="E57">
+      <c r="G57">
         <v>12</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>SIMPSON, 1912</t>
         </is>
       </c>
-      <c r="O57">
+      <c r="Q57">
         <v>10</v>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>PETRAS and LEHMAN, 1966</t>
         </is>
@@ -2679,56 +3224,66 @@
           <t>Rat (unspecified)</t>
         </is>
       </c>
-      <c r="D58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Iwaniuk_etal_1999_imputed</t>
+        </is>
+      </c>
+      <c r="F58">
         <v>3</v>
       </c>
-      <c r="E58">
+      <c r="G58">
         <v>0.4</v>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>137000</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>BROWN, 1971</t>
         </is>
       </c>
-      <c r="H58">
+      <c r="J58">
         <v>5</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>BISHOP et al., 1971</t>
         </is>
       </c>
-      <c r="J58">
+      <c r="L58">
         <v>0.1</v>
       </c>
-      <c r="K58">
+      <c r="M58">
         <v>0.14</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>GOODMAN et al., 1966</t>
         </is>
       </c>
-      <c r="O58">
+      <c r="Q58">
         <v>8</v>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>GOODMAN et al., 1966</t>
         </is>
       </c>
-      <c r="Q58">
+      <c r="S58">
         <v>5</v>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>BROWN, 1971</t>
         </is>
@@ -2745,37 +3300,47 @@
           <t>Procavia capensis</t>
         </is>
       </c>
-      <c r="D59">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Procavia capensis</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F59">
         <v>2</v>
       </c>
-      <c r="E59">
+      <c r="G59">
         <v>17</v>
       </c>
-      <c r="H59">
+      <c r="J59">
         <v>9</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>VERHAART, 1967</t>
         </is>
       </c>
-      <c r="K59">
+      <c r="M59">
         <v>0.72</v>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>VERHAART, 1967</t>
         </is>
       </c>
-      <c r="Q59">
+      <c r="S59">
         <v>6</v>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>VERHAART, 1967</t>
         </is>
@@ -2792,32 +3357,42 @@
           <t>Callorhinus ursinus</t>
         </is>
       </c>
-      <c r="D60">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Callorhinus ursinus</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F60">
         <v>1</v>
       </c>
-      <c r="E60">
+      <c r="G60">
         <v>52</v>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>748000</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>LASSEK and KARLSBERG, 1956</t>
         </is>
       </c>
-      <c r="H60">
+      <c r="J60">
         <v>25</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>LASSEK and KARLSBERG, 1956</t>
         </is>
       </c>
-      <c r="J60">
+      <c r="L60">
         <v>0.27</v>
       </c>
-      <c r="K60">
+      <c r="M60">
         <v>2.08</v>
       </c>
     </row>
@@ -2832,48 +3407,58 @@
           <t>Ovis aries</t>
         </is>
       </c>
-      <c r="D61">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ovis aries</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F61">
         <v>1</v>
       </c>
-      <c r="E61">
+      <c r="G61">
         <v>80</v>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>238000</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="H61">
+      <c r="J61">
         <v>5</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="J61">
+      <c r="L61">
         <v>0.59</v>
       </c>
-      <c r="K61">
+      <c r="M61">
         <v>1.42</v>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>KING, 1911</t>
         </is>
       </c>
-      <c r="Q61">
+      <c r="S61">
         <v>6</v>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>KING, 1911</t>
         </is>
@@ -2890,45 +3475,55 @@
           <t>Nycticebus coucang</t>
         </is>
       </c>
-      <c r="D62">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Nycticebus coucang</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F62">
         <v>5</v>
       </c>
-      <c r="E62">
+      <c r="G62">
         <v>1.3</v>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>4.5</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K62">
+      <c r="M62">
         <v>0.28</v>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>CAMPBELL, 1967</t>
         </is>
       </c>
-      <c r="O62">
+      <c r="Q62">
         <v>10</v>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>CAMPBELL et al., 1966</t>
         </is>
       </c>
-      <c r="Q62">
+      <c r="S62">
         <v>6</v>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>CAMPBELL et al., 1966</t>
         </is>
@@ -2942,24 +3537,34 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Tachyglossus aculeatus</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>Tachyglossus aculeata</t>
         </is>
       </c>
-      <c r="D63">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F63">
         <v>2</v>
       </c>
-      <c r="E63">
+      <c r="G63">
         <v>4.2</v>
       </c>
-      <c r="K63">
+      <c r="M63">
         <v>0.39</v>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>T16</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>GOLDBY, 1939</t>
         </is>
@@ -2973,24 +3578,34 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Sciurus hudsonius</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>Sciurrrus hudsonius</t>
         </is>
       </c>
-      <c r="D64">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F64">
         <v>3</v>
       </c>
-      <c r="E64">
+      <c r="G64">
         <v>0.6</v>
       </c>
-      <c r="K64">
+      <c r="M64">
         <v>0.4</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>SIMPSON, 1914</t>
         </is>
@@ -3007,21 +3622,31 @@
           <t>Tapirus</t>
         </is>
       </c>
-      <c r="D65">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Tapirus</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F65">
         <v>1</v>
       </c>
-      <c r="E65">
+      <c r="G65">
         <v>250</v>
       </c>
-      <c r="H65">
+      <c r="J65">
         <v>5</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K65">
+      <c r="M65">
         <v>1.48</v>
       </c>
     </row>
@@ -3036,13 +3661,23 @@
           <t>Tarsius</t>
         </is>
       </c>
-      <c r="D66">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Tarsius</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F66">
         <v>4</v>
       </c>
-      <c r="E66">
+      <c r="G66">
         <v>0.12</v>
       </c>
-      <c r="K66">
+      <c r="M66">
         <v>0.16</v>
       </c>
     </row>
@@ -3057,34 +3692,44 @@
           <t>Potorous apicalis</t>
         </is>
       </c>
-      <c r="D67">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Potorous apicalis</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F67">
         <v>2</v>
       </c>
-      <c r="E67">
+      <c r="G67">
         <v>1.35</v>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>T12</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>MARTIN et al., 1972</t>
         </is>
       </c>
-      <c r="O67">
+      <c r="Q67">
         <v>7</v>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>MARTIN et al., 1972</t>
         </is>
       </c>
-      <c r="Q67">
+      <c r="S67">
         <v>5</v>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>MARTIN et al., 1972</t>
         </is>
@@ -3106,45 +3751,55 @@
           <t>Tupaia glis</t>
         </is>
       </c>
-      <c r="D68">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tupaia glis</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="F68">
         <v>3</v>
       </c>
-      <c r="E68">
+      <c r="G68">
         <v>0.16</v>
       </c>
-      <c r="H68">
+      <c r="J68">
         <v>2</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
       </c>
-      <c r="K68">
+      <c r="M68">
         <v>0.12</v>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Lower T</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>SHRIVER and NOBACK, 1967</t>
         </is>
       </c>
-      <c r="O68">
+      <c r="Q68">
         <v>6</v>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>JANE et al., 1969</t>
         </is>
       </c>
-      <c r="Q68">
+      <c r="S68">
         <v>5</v>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>CAMPBELL, 1967</t>
         </is>
@@ -3158,24 +3813,34 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>Phocoena phocoena</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>Phocaena phocoena</t>
         </is>
       </c>
-      <c r="D69">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>spelling_correction</t>
+        </is>
+      </c>
+      <c r="F69">
         <v>1</v>
       </c>
-      <c r="E69">
+      <c r="G69">
         <v>60</v>
       </c>
-      <c r="H69">
+      <c r="J69">
         <v>5</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="K69">
+      <c r="M69">
         <v>1.27</v>
       </c>
     </row>
@@ -3190,18 +3855,28 @@
           <t>Marmota monax</t>
         </is>
       </c>
-      <c r="E70">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Marmota monax</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>as_printed</t>
+        </is>
+      </c>
+      <c r="G70">
         <v>5.3</v>
       </c>
-      <c r="K70">
+      <c r="M70">
         <v>0.37</v>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>DOUGLAS and BARR, 1950</t>
         </is>
@@ -3488,13 +4163,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA347322-1114-46EB-A864-8459E9E73C9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4FE2300-06AE-4850-A753-EF26EA22A95D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF181F5B-F7BF-426F-A746-5C764CC0D6B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36704499-27A1-4F88-BB71-C753FE6C407A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{192B76C3-FD29-41AB-ACBA-ED782030CC31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F038FE7E-C0EE-4F89-A2B6-125993CA7633}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -382,75 +382,70 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Digital dexterity</t>
+          <t>Body weight kg</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Body weight kg</t>
+          <t>Number of fibers per tract</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Number of fibers per tract</t>
+          <t>Number of fibers per tract ref</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Number of fibers per tract ref</t>
+          <t>Largest fiber diameter µm</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Largest fiber diameter µm</t>
+          <t>Largest fiber diameter µm ref</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Largest fiber diameter µm ref</t>
+          <t>Average fiber size x 10ˆ5 K</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Average fiber size x 10ˆ5 K</t>
+          <t>Area of tract mmˆ2</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Area of tract mmˆ2</t>
+          <t>Area of tract mmˆ2 ref</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Area of tract mmˆ2 ref</t>
+          <t>Penetration down spinal cord</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Penetration down spinal cord</t>
+          <t>Penetration down spinal cord ref</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Penetration down spinal cord ref</t>
+          <t>Lamina of axon terminals deepest</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Lamina of axon terminals deepest</t>
+          <t>Lamina of axon terminals deepest ref</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Lamina of axon terminals deepest ref</t>
+          <t>Lamina of axon terminals densest</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Lamina of axon terminals densest</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Lamina of axon terminals densest ref</t>
         </is>
@@ -478,20 +473,17 @@
         </is>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
         <v>60</v>
       </c>
-      <c r="M2">
+      <c r="L2">
         <v>0.53</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Upper C</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>Upper C</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
@@ -519,20 +511,17 @@
         </is>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
         <v>20</v>
       </c>
-      <c r="J3">
+      <c r="I3">
         <v>10</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M3">
+      <c r="L3">
         <v>0.6</v>
       </c>
     </row>
@@ -563,41 +552,38 @@
         </is>
       </c>
       <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M4">
+      <c r="L4">
         <v>0.6</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
           <t>FISHER el al., 1969</t>
         </is>
       </c>
-      <c r="Q4">
+      <c r="P4">
         <v>8</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>FISHER el al., 1969</t>
         </is>
       </c>
-      <c r="S4">
+      <c r="R4">
         <v>6</v>
       </c>
     </row>
@@ -623,12 +609,9 @@
         </is>
       </c>
       <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
         <v>0.033</v>
       </c>
-      <c r="M5">
+      <c r="L5">
         <v>0.01</v>
       </c>
     </row>
@@ -654,12 +637,9 @@
         </is>
       </c>
       <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
         <v>0.01</v>
       </c>
-      <c r="M6">
+      <c r="L6">
         <v>0.04</v>
       </c>
     </row>
@@ -685,20 +665,17 @@
         </is>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
         <v>0.03</v>
       </c>
-      <c r="M7">
+      <c r="L7">
         <v>0.01</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
         <is>
           <t>BROERE, 1966</t>
         </is>
@@ -726,12 +703,9 @@
         </is>
       </c>
       <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
         <v>0.9</v>
       </c>
-      <c r="M8">
+      <c r="L8">
         <v>0.12</v>
       </c>
     </row>
@@ -757,12 +731,9 @@
         </is>
       </c>
       <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
         <v>0.016</v>
       </c>
-      <c r="M9">
+      <c r="L9">
         <v>0.01</v>
       </c>
     </row>
@@ -788,18 +759,15 @@
         </is>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G10">
-        <v>1.3</v>
-      </c>
-      <c r="H10">
         <v>8000</v>
       </c>
+      <c r="K10">
+        <v>0.25</v>
+      </c>
       <c r="L10">
-        <v>0.25</v>
-      </c>
-      <c r="M10">
         <v>0.02</v>
       </c>
     </row>
@@ -815,12 +783,9 @@
         </is>
       </c>
       <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
         <v>200</v>
       </c>
-      <c r="M11">
+      <c r="L11">
         <v>9.210000000000001</v>
       </c>
     </row>
@@ -846,17 +811,14 @@
         </is>
       </c>
       <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12">
         <v>13</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
         <is>
           <t>DOUGLAS and BARR, 1950</t>
         </is>
@@ -889,33 +851,30 @@
         </is>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="G13">
         <v>1.14</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
           <t>FERRER, 1971</t>
         </is>
       </c>
-      <c r="Q13">
+      <c r="P13">
         <v>9</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>FERRER, 1971</t>
         </is>
       </c>
-      <c r="S13">
+      <c r="R13">
         <v>6</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>FERRER, 1971</t>
         </is>
@@ -943,25 +902,22 @@
         </is>
       </c>
       <c r="F14">
-        <v>5</v>
-      </c>
-      <c r="G14">
         <v>0.26</v>
       </c>
-      <c r="J14">
+      <c r="I14">
         <v>2.5</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Lower L</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
-        <is>
-          <t>Lower L</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
@@ -989,15 +945,12 @@
         </is>
       </c>
       <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
         <v>570</v>
       </c>
-      <c r="J15">
+      <c r="I15">
         <v>6</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
@@ -1030,55 +983,52 @@
         </is>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G16">
-        <v>3.5</v>
-      </c>
-      <c r="H16">
         <v>186000</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
-      <c r="J16">
+      <c r="I16">
         <v>5</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>SCHIEBEL and SCHIEBEL, 1966</t>
         </is>
       </c>
+      <c r="K16">
+        <v>0.6</v>
+      </c>
       <c r="L16">
-        <v>0.6</v>
-      </c>
-      <c r="M16">
         <v>1.13</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
           <t>NYBERG-HANSEN and BRODAL, 1963</t>
         </is>
       </c>
-      <c r="Q16">
+      <c r="P16">
         <v>8</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>NYBERG-HANSEN and BRODAL, 1963</t>
         </is>
       </c>
-      <c r="S16">
+      <c r="R16">
         <v>6</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>NYBERG-HANSEN and BRODAL, 1963</t>
         </is>
@@ -1111,47 +1061,44 @@
         </is>
       </c>
       <c r="F17">
+        <v>44</v>
+      </c>
+      <c r="G17">
+        <v>807000</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LASSEK and WHEATLEY, 1945</t>
+        </is>
+      </c>
+      <c r="K17">
+        <v>0.96</v>
+      </c>
+      <c r="L17">
+        <v>7.77</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>coccygeal</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>PETRAS, 1968</t>
+        </is>
+      </c>
+      <c r="P17">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>PETRAS, 1968</t>
+        </is>
+      </c>
+      <c r="R17">
         <v>6</v>
       </c>
-      <c r="G17">
-        <v>44</v>
-      </c>
-      <c r="H17">
-        <v>807000</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>LASSEK and WHEATLEY, 1945</t>
-        </is>
-      </c>
-      <c r="L17">
-        <v>0.96</v>
-      </c>
-      <c r="M17">
-        <v>7.77</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>coccygeal</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>PETRAS, 1968</t>
-        </is>
-      </c>
-      <c r="Q17">
-        <v>10</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>PETRAS, 1968</t>
-        </is>
-      </c>
-      <c r="S17">
-        <v>6</v>
-      </c>
-      <c r="T17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -1179,20 +1126,17 @@
         </is>
       </c>
       <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18">
         <v>0.1</v>
       </c>
-      <c r="M18">
+      <c r="L18">
         <v>0.26</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
         <is>
           <t>SIMPSON, 1914</t>
         </is>
@@ -1210,39 +1154,36 @@
         </is>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G19">
-        <v>500</v>
-      </c>
-      <c r="H19">
         <v>540000</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="J19">
+      <c r="I19">
         <v>5</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
+      <c r="K19">
+        <v>0.55</v>
+      </c>
       <c r="L19">
-        <v>0.55</v>
-      </c>
-      <c r="M19">
         <v>2.97</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Upper C</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
-        <is>
-          <t>Upper C</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
@@ -1270,36 +1211,33 @@
         </is>
       </c>
       <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
-      <c r="J20">
+      <c r="I20">
         <v>8</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>GOLDBY and KACKER, 1963</t>
         </is>
       </c>
-      <c r="M20">
+      <c r="L20">
         <v>0.37</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
           <t>GOLDBY and KACKER, 1963</t>
         </is>
       </c>
-      <c r="Q20">
+      <c r="P20">
         <v>6</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>GOLDBY and KACKER, 1963</t>
         </is>
@@ -1317,39 +1255,36 @@
         </is>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="G21">
-        <v>200</v>
-      </c>
-      <c r="H21">
         <v>490000</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="J21">
+      <c r="I21">
         <v>6</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
+      <c r="K21">
+        <v>0.58</v>
+      </c>
       <c r="L21">
-        <v>0.58</v>
-      </c>
-      <c r="M21">
         <v>2.89</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Upper C</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
-        <is>
-          <t>Upper C</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
@@ -1382,39 +1317,36 @@
         </is>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>11</v>
-      </c>
-      <c r="H22">
         <v>285500</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
+      <c r="K22">
+        <v>1.22</v>
+      </c>
       <c r="L22">
-        <v>1.22</v>
-      </c>
-      <c r="M22">
         <v>3.49</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
           <t>BUXTON and GOODMAN, 1967</t>
         </is>
       </c>
-      <c r="Q22">
+      <c r="P22">
         <v>8</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>BUXTON and GOODMAN, 1967</t>
         </is>
@@ -1442,28 +1374,25 @@
         </is>
       </c>
       <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
         <v>6000</v>
       </c>
-      <c r="J23">
+      <c r="I23">
         <v>8</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>VERHAART, 1963</t>
         </is>
       </c>
-      <c r="M23">
+      <c r="L23">
         <v>5.13</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Middle T</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
-        <is>
-          <t>Middle T</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
         <is>
           <t>VERHAART, 1963</t>
         </is>
@@ -1496,28 +1425,25 @@
         </is>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="G24">
-        <v>0.9</v>
-      </c>
-      <c r="H24">
         <v>90000</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>NOORDUYN, 1959</t>
         </is>
       </c>
-      <c r="J24">
+      <c r="I24">
         <v>10</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>NOORDUYN, 1959</t>
         </is>
       </c>
-      <c r="M24">
+      <c r="L24">
         <v>1.5</v>
       </c>
     </row>
@@ -1546,52 +1472,49 @@
         <v>6</v>
       </c>
       <c r="G25">
+        <v>315000</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>VERHAART, 1948b</t>
+        </is>
+      </c>
+      <c r="I25">
+        <v>12</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VERHAART, 1970</t>
+        </is>
+      </c>
+      <c r="K25">
+        <v>1.09</v>
+      </c>
+      <c r="L25">
+        <v>3.44</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>PETRAS, 1968</t>
+        </is>
+      </c>
+      <c r="P25">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>PETRAS, 1968</t>
+        </is>
+      </c>
+      <c r="R25">
         <v>6</v>
       </c>
-      <c r="H25">
-        <v>315000</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>VERHAART, 1948b</t>
-        </is>
-      </c>
-      <c r="J25">
-        <v>12</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>VERHAART, 1970</t>
-        </is>
-      </c>
-      <c r="L25">
-        <v>1.09</v>
-      </c>
-      <c r="M25">
-        <v>3.44</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>PETRAS, 1968</t>
-        </is>
-      </c>
-      <c r="Q25">
-        <v>10</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>PETRAS, 1968</t>
-        </is>
-      </c>
-      <c r="S25">
-        <v>6</v>
-      </c>
-      <c r="T25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -1619,23 +1542,20 @@
         </is>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>10</v>
-      </c>
-      <c r="H26">
         <v>239700</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>VERHAART, 1948b</t>
         </is>
       </c>
+      <c r="K26">
+        <v>1.35</v>
+      </c>
       <c r="L26">
-        <v>1.35</v>
-      </c>
-      <c r="M26">
         <v>3.25</v>
       </c>
     </row>
@@ -1661,47 +1581,44 @@
         </is>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G27">
-        <v>80</v>
-      </c>
-      <c r="H27">
         <v>260000</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="J27">
+      <c r="I27">
         <v>5</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
+      <c r="K27">
+        <v>0.21</v>
+      </c>
       <c r="L27">
-        <v>0.21</v>
-      </c>
-      <c r="M27">
         <v>0.569</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>C7</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
           <t>HAARTSEN and VERHAART, 1967</t>
         </is>
       </c>
-      <c r="Q27">
+      <c r="P27">
         <v>6</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>HAARTSEN and VERHAART, 1967</t>
         </is>
@@ -1729,17 +1646,14 @@
         </is>
       </c>
       <c r="F28">
-        <v>3</v>
-      </c>
-      <c r="G28">
         <v>0.65</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
         <is>
           <t>SIMPSON,1915</t>
         </is>
@@ -1767,12 +1681,9 @@
         </is>
       </c>
       <c r="F29">
-        <v>2</v>
-      </c>
-      <c r="G29">
         <v>0.6</v>
       </c>
-      <c r="M29">
+      <c r="L29">
         <v>0.33</v>
       </c>
     </row>
@@ -1798,25 +1709,22 @@
         </is>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="G30">
-        <v>0.5</v>
-      </c>
-      <c r="H30">
         <v>480000</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>DOUGLAS and BARR, 1950</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
         <is>
           <t>DOUGLAS and BARR, 1950</t>
         </is>
@@ -1844,20 +1752,17 @@
         </is>
       </c>
       <c r="F31">
-        <v>2</v>
-      </c>
-      <c r="G31">
         <v>0.75</v>
       </c>
-      <c r="M31">
+      <c r="L31">
         <v>0.02</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Upper C</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
-        <is>
-          <t>Upper C</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
@@ -1885,17 +1790,14 @@
         </is>
       </c>
       <c r="F32">
-        <v>2</v>
-      </c>
-      <c r="G32">
         <v>0.5</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Upper C</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
-        <is>
-          <t>Upper C</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
         <is>
           <t>ROBARDS, personal commun.; CAMPBELL, 1967</t>
         </is>
@@ -1928,31 +1830,28 @@
         </is>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="G33">
-        <v>90</v>
-      </c>
-      <c r="H33">
         <v>210000</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="J33">
+      <c r="I33">
         <v>5</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
+      <c r="K33">
+        <v>0.85</v>
+      </c>
       <c r="L33">
-        <v>0.85</v>
-      </c>
-      <c r="M33">
         <v>1.8</v>
       </c>
     </row>
@@ -1978,20 +1877,17 @@
         </is>
       </c>
       <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34">
         <v>350</v>
       </c>
-      <c r="J34">
+      <c r="I34">
         <v>5</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M34">
+      <c r="L34">
         <v>2.68</v>
       </c>
     </row>
@@ -2017,25 +1913,22 @@
         </is>
       </c>
       <c r="F35">
-        <v>3</v>
-      </c>
-      <c r="G35">
         <v>2.1</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Lower L</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Lower L</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
           <t>HARTING and NOBACK, 1970</t>
         </is>
       </c>
-      <c r="Q35">
+      <c r="P35">
         <v>10</v>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>HARTING and NOBACK, 1970</t>
         </is>
@@ -2063,25 +1956,22 @@
         </is>
       </c>
       <c r="F36">
-        <v>5</v>
-      </c>
-      <c r="G36">
         <v>2.1</v>
       </c>
-      <c r="J36">
+      <c r="I36">
         <v>3</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Lower L</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
-        <is>
-          <t>Lower L</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
@@ -2114,39 +2004,36 @@
         </is>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="G37">
-        <v>70</v>
-      </c>
-      <c r="H37">
         <v>1101000</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
-      <c r="J37">
+      <c r="I37">
         <v>22</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>TRUEX and CARPENTER, 1969</t>
         </is>
       </c>
+      <c r="K37">
+        <v>1.03</v>
+      </c>
       <c r="L37">
-        <v>1.03</v>
-      </c>
-      <c r="M37">
         <v>11.43</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>coccygeal</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
-        <is>
-          <t>coccygeal</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
         <is>
           <t>TRUEX and CARPENTER, 1969</t>
         </is>
@@ -2174,28 +2061,25 @@
         </is>
       </c>
       <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38">
         <v>0.1</v>
       </c>
-      <c r="J38">
+      <c r="I38">
         <v>4</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>BISHOP et al., 1971</t>
         </is>
       </c>
-      <c r="M38">
+      <c r="L38">
         <v>0.01</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Upper T</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
-        <is>
-          <t>Upper T</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
         <is>
           <t>LINOWIECKI, 1914</t>
         </is>
@@ -2223,55 +2107,52 @@
         </is>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G39">
+        <v>505000</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>LASSEK, 1943</t>
+        </is>
+      </c>
+      <c r="I39">
+        <v>12</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>LASSEK, 1943</t>
+        </is>
+      </c>
+      <c r="K39">
+        <v>0.63</v>
+      </c>
+      <c r="L39">
+        <v>3.23</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>coccygeal</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>PETRAS, 1968</t>
+        </is>
+      </c>
+      <c r="P39">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>PETRAS, 1969</t>
+        </is>
+      </c>
+      <c r="R39">
         <v>6</v>
       </c>
-      <c r="H39">
-        <v>505000</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>LASSEK, 1943</t>
-        </is>
-      </c>
-      <c r="J39">
-        <v>12</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>LASSEK, 1943</t>
-        </is>
-      </c>
-      <c r="L39">
-        <v>0.63</v>
-      </c>
-      <c r="M39">
-        <v>3.23</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>coccygeal</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>PETRAS, 1968</t>
-        </is>
-      </c>
-      <c r="Q39">
-        <v>10</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>PETRAS, 1969</t>
-        </is>
-      </c>
-      <c r="S39">
-        <v>6</v>
-      </c>
-      <c r="T39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -2304,36 +2185,33 @@
         </is>
       </c>
       <c r="F40">
-        <v>5</v>
-      </c>
-      <c r="G40">
         <v>1.25</v>
       </c>
-      <c r="M40">
+      <c r="L40">
         <v>2</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>coccygeal</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>coccygeal</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="Q40">
+      <c r="P40">
         <v>10</v>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>PETRAS, 1969</t>
         </is>
       </c>
-      <c r="S40">
+      <c r="R40">
         <v>6</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -2366,33 +2244,30 @@
         </is>
       </c>
       <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>coccygeal</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>PETRAS, 1968</t>
+        </is>
+      </c>
+      <c r="P41">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>PETRAS, 1969</t>
+        </is>
+      </c>
+      <c r="R41">
         <v>6</v>
       </c>
-      <c r="G41">
-        <v>4</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>coccygeal</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>PETRAS, 1968</t>
-        </is>
-      </c>
-      <c r="Q41">
-        <v>10</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>PETRAS, 1969</t>
-        </is>
-      </c>
-      <c r="S41">
-        <v>6</v>
-      </c>
-      <c r="T41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -2420,33 +2295,30 @@
         </is>
       </c>
       <c r="F42">
-        <v>5</v>
-      </c>
-      <c r="G42">
         <v>6</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>coccygeal</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>coccygeal</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="Q42">
+      <c r="P42">
         <v>10</v>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
       </c>
-      <c r="S42">
+      <c r="R42">
         <v>6</v>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -2474,23 +2346,20 @@
         </is>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>5</v>
-      </c>
-      <c r="H43">
         <v>195000</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>VERHAART, 1948a</t>
         </is>
       </c>
+      <c r="K43">
+        <v>0.6</v>
+      </c>
       <c r="L43">
-        <v>0.6</v>
-      </c>
-      <c r="M43">
         <v>1.18</v>
       </c>
     </row>
@@ -2521,47 +2390,44 @@
         </is>
       </c>
       <c r="F44">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G44">
+        <v>400000</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>DEMEYER and RUSSEL, 1958</t>
+        </is>
+      </c>
+      <c r="K44">
+        <v>0.72</v>
+      </c>
+      <c r="L44">
+        <v>2.89</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>coccygeal</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>PETRAS, 1968</t>
+        </is>
+      </c>
+      <c r="P44">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>PETRAS, 1969</t>
+        </is>
+      </c>
+      <c r="R44">
         <v>6</v>
       </c>
-      <c r="G44">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H44">
-        <v>400000</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>DEMEYER and RUSSEL, 1958</t>
-        </is>
-      </c>
-      <c r="L44">
-        <v>0.72</v>
-      </c>
-      <c r="M44">
-        <v>2.89</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>coccygeal</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>PETRAS, 1968</t>
-        </is>
-      </c>
-      <c r="Q44">
-        <v>10</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>PETRAS, 1969</t>
-        </is>
-      </c>
-      <c r="S44">
-        <v>6</v>
-      </c>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>PETRAS, 1968</t>
         </is>
@@ -2594,15 +2460,12 @@
         </is>
       </c>
       <c r="F45">
-        <v>6</v>
-      </c>
-      <c r="G45">
         <v>25</v>
       </c>
-      <c r="Q45">
+      <c r="P45">
         <v>10</v>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>PHILLIPS, 1967</t>
         </is>
@@ -2630,25 +2493,22 @@
         </is>
       </c>
       <c r="F46">
-        <v>4</v>
-      </c>
-      <c r="G46">
         <v>0.4</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
           <t>SHRIVER and MATZKE, 1965</t>
         </is>
       </c>
-      <c r="Q46">
+      <c r="P46">
         <v>6</v>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>SHRIVER and MATZKE, 1965</t>
         </is>
@@ -2681,44 +2541,41 @@
         </is>
       </c>
       <c r="F47">
-        <v>5</v>
-      </c>
-      <c r="G47">
         <v>0.75</v>
       </c>
-      <c r="J47">
+      <c r="I47">
         <v>8</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M47">
+      <c r="L47">
         <v>0.7</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
           <t>VERHAART, 1966</t>
         </is>
       </c>
-      <c r="Q47">
+      <c r="P47">
         <v>9</v>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>HARTING AND NOBACK, 1970</t>
         </is>
       </c>
-      <c r="S47">
+      <c r="R47">
         <v>6</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>HARTING AND NOBACK, 1970</t>
         </is>
@@ -2741,23 +2598,20 @@
         </is>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>0.025</v>
       </c>
       <c r="G48">
-        <v>0.025</v>
-      </c>
-      <c r="H48">
         <v>32300</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
+      <c r="K48">
+        <v>0.21</v>
+      </c>
       <c r="L48">
-        <v>0.21</v>
-      </c>
-      <c r="M48">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -2783,31 +2637,28 @@
         </is>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="G49">
-        <v>250</v>
-      </c>
-      <c r="H49">
         <v>412000</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="J49">
+      <c r="I49">
         <v>5</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
+      <c r="K49">
+        <v>0.9</v>
+      </c>
       <c r="L49">
-        <v>0.9</v>
-      </c>
-      <c r="M49">
         <v>3.74</v>
       </c>
     </row>
@@ -2833,47 +2684,44 @@
         </is>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="G50">
-        <v>3.7</v>
-      </c>
-      <c r="H50">
         <v>48100</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>TOWE, 1973</t>
         </is>
       </c>
+      <c r="K50">
+        <v>0.45</v>
+      </c>
       <c r="L50">
-        <v>0.45</v>
-      </c>
-      <c r="M50">
         <v>0.22</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Upper T</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Upper T</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
           <t>BAUTISTA and MATZKE, 1965</t>
         </is>
       </c>
-      <c r="Q50">
+      <c r="P50">
         <v>8</v>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>MARTIN and FISHER, 1968</t>
         </is>
       </c>
-      <c r="S50">
+      <c r="R50">
         <v>5</v>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>MARTIN and FISHER, 1968</t>
         </is>
@@ -2901,12 +2749,9 @@
         </is>
       </c>
       <c r="F51">
-        <v>6</v>
-      </c>
-      <c r="G51">
         <v>60</v>
       </c>
-      <c r="M51">
+      <c r="L51">
         <v>2.61</v>
       </c>
     </row>
@@ -2932,20 +2777,17 @@
         </is>
       </c>
       <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52">
         <v>18</v>
       </c>
-      <c r="J52">
+      <c r="I52">
         <v>2.5</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M52">
+      <c r="L52">
         <v>0.16</v>
       </c>
     </row>
@@ -2971,36 +2813,33 @@
         </is>
       </c>
       <c r="F53">
-        <v>3</v>
-      </c>
-      <c r="G53">
         <v>3.5</v>
       </c>
-      <c r="M53">
+      <c r="L53">
         <v>0.54</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Lower T</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Lower T</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
           <t>REES and HORE, 1970; MARTIN et al., 1970</t>
         </is>
       </c>
-      <c r="Q53">
+      <c r="P53">
         <v>8</v>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>REES and HORE, 1970; MARTIN et al., 1970</t>
         </is>
       </c>
-      <c r="S53">
+      <c r="R53">
         <v>6</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>REES and HORE, 1970; MARTIN et al., 1970</t>
         </is>
@@ -3028,20 +2867,17 @@
         </is>
       </c>
       <c r="F54">
-        <v>2</v>
-      </c>
-      <c r="G54">
         <v>0.003</v>
       </c>
-      <c r="J54">
+      <c r="I54">
         <v>1</v>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M54">
+      <c r="L54">
         <v>0.02</v>
       </c>
     </row>
@@ -3067,36 +2903,33 @@
         </is>
       </c>
       <c r="F55">
-        <v>3</v>
-      </c>
-      <c r="G55">
         <v>3.5</v>
       </c>
-      <c r="M55">
+      <c r="L55">
         <v>0.1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>T7</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
           <t>WATSON, 1971</t>
         </is>
       </c>
-      <c r="Q55">
+      <c r="P55">
         <v>6</v>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>WATSON, 1971</t>
         </is>
       </c>
-      <c r="S55">
+      <c r="R55">
         <v>5</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>WATSON, 1971</t>
         </is>
@@ -3129,39 +2962,36 @@
         </is>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G56">
-        <v>1.8</v>
-      </c>
-      <c r="H56">
         <v>101700</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>LASSEK and RASMUSSEN, 1940</t>
         </is>
       </c>
-      <c r="J56">
+      <c r="I56">
         <v>4</v>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
+      <c r="K56">
+        <v>0.27</v>
+      </c>
       <c r="L56">
-        <v>0.27</v>
-      </c>
-      <c r="M56">
         <v>0.28</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
@@ -3189,25 +3019,22 @@
         </is>
       </c>
       <c r="F57">
-        <v>3</v>
-      </c>
-      <c r="G57">
         <v>12</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
           <t>SIMPSON, 1912</t>
         </is>
       </c>
-      <c r="Q57">
+      <c r="P57">
         <v>10</v>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>PETRAS and LEHMAN, 1966</t>
         </is>
@@ -3235,55 +3062,52 @@
         </is>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="G58">
-        <v>0.4</v>
-      </c>
-      <c r="H58">
         <v>137000</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>BROWN, 1971</t>
         </is>
       </c>
-      <c r="J58">
+      <c r="I58">
         <v>5</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>BISHOP et al., 1971</t>
         </is>
       </c>
+      <c r="K58">
+        <v>0.1</v>
+      </c>
       <c r="L58">
-        <v>0.1</v>
-      </c>
-      <c r="M58">
         <v>0.14</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
           <t>GOODMAN et al., 1966</t>
         </is>
       </c>
-      <c r="Q58">
+      <c r="P58">
         <v>8</v>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>GOODMAN et al., 1966</t>
         </is>
       </c>
-      <c r="S58">
+      <c r="R58">
         <v>5</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>BROWN, 1971</t>
         </is>
@@ -3311,36 +3135,33 @@
         </is>
       </c>
       <c r="F59">
-        <v>2</v>
-      </c>
-      <c r="G59">
         <v>17</v>
       </c>
-      <c r="J59">
+      <c r="I59">
         <v>9</v>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>VERHAART, 1967</t>
         </is>
       </c>
-      <c r="M59">
+      <c r="L59">
         <v>0.72</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
           <t>VERHAART, 1967</t>
         </is>
       </c>
-      <c r="S59">
+      <c r="R59">
         <v>6</v>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>VERHAART, 1967</t>
         </is>
@@ -3368,31 +3189,28 @@
         </is>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="G60">
-        <v>52</v>
-      </c>
-      <c r="H60">
         <v>748000</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>LASSEK and KARLSBERG, 1956</t>
         </is>
       </c>
-      <c r="J60">
+      <c r="I60">
         <v>25</v>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>LASSEK and KARLSBERG, 1956</t>
         </is>
       </c>
+      <c r="K60">
+        <v>0.27</v>
+      </c>
       <c r="L60">
-        <v>0.27</v>
-      </c>
-      <c r="M60">
         <v>2.08</v>
       </c>
     </row>
@@ -3418,47 +3236,44 @@
         </is>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G61">
-        <v>80</v>
-      </c>
-      <c r="H61">
         <v>238000</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>LASSEK, 1942</t>
         </is>
       </c>
-      <c r="J61">
+      <c r="I61">
         <v>5</v>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
+      <c r="K61">
+        <v>0.59</v>
+      </c>
       <c r="L61">
-        <v>0.59</v>
-      </c>
-      <c r="M61">
         <v>1.42</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
           <t>KING, 1911</t>
         </is>
       </c>
-      <c r="S61">
+      <c r="R61">
         <v>6</v>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>KING, 1911</t>
         </is>
@@ -3486,44 +3301,41 @@
         </is>
       </c>
       <c r="F62">
-        <v>5</v>
-      </c>
-      <c r="G62">
         <v>1.3</v>
       </c>
-      <c r="J62">
+      <c r="I62">
         <v>4.5</v>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M62">
+      <c r="L62">
         <v>0.28</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
           <t>CAMPBELL, 1967</t>
         </is>
       </c>
-      <c r="Q62">
+      <c r="P62">
         <v>10</v>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>CAMPBELL et al., 1966</t>
         </is>
       </c>
-      <c r="S62">
+      <c r="R62">
         <v>6</v>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>CAMPBELL et al., 1966</t>
         </is>
@@ -3551,20 +3363,17 @@
         </is>
       </c>
       <c r="F63">
-        <v>2</v>
-      </c>
-      <c r="G63">
         <v>4.2</v>
       </c>
-      <c r="M63">
+      <c r="L63">
         <v>0.39</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
-        <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
         <is>
           <t>GOLDBY, 1939</t>
         </is>
@@ -3592,20 +3401,17 @@
         </is>
       </c>
       <c r="F64">
-        <v>3</v>
-      </c>
-      <c r="G64">
         <v>0.6</v>
       </c>
-      <c r="M64">
+      <c r="L64">
         <v>0.4</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
         <is>
           <t>SIMPSON, 1914</t>
         </is>
@@ -3633,20 +3439,17 @@
         </is>
       </c>
       <c r="F65">
-        <v>1</v>
-      </c>
-      <c r="G65">
         <v>250</v>
       </c>
-      <c r="J65">
+      <c r="I65">
         <v>5</v>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M65">
+      <c r="L65">
         <v>1.48</v>
       </c>
     </row>
@@ -3672,12 +3475,9 @@
         </is>
       </c>
       <c r="F66">
-        <v>4</v>
-      </c>
-      <c r="G66">
         <v>0.12</v>
       </c>
-      <c r="M66">
+      <c r="L66">
         <v>0.16</v>
       </c>
     </row>
@@ -3703,33 +3503,30 @@
         </is>
       </c>
       <c r="F67">
-        <v>2</v>
-      </c>
-      <c r="G67">
         <v>1.35</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
           <t>MARTIN et al., 1972</t>
         </is>
       </c>
-      <c r="Q67">
+      <c r="P67">
         <v>7</v>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>MARTIN et al., 1972</t>
         </is>
       </c>
-      <c r="S67">
+      <c r="R67">
         <v>5</v>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>MARTIN et al., 1972</t>
         </is>
@@ -3762,44 +3559,41 @@
         </is>
       </c>
       <c r="F68">
-        <v>3</v>
-      </c>
-      <c r="G68">
         <v>0.16</v>
       </c>
-      <c r="J68">
+      <c r="I68">
         <v>2</v>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>VERHAART, 1966</t>
         </is>
       </c>
-      <c r="M68">
+      <c r="L68">
         <v>0.12</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Lower T</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Lower T</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
           <t>SHRIVER and NOBACK, 1967</t>
         </is>
       </c>
-      <c r="Q68">
+      <c r="P68">
         <v>6</v>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>JANE et al., 1969</t>
         </is>
       </c>
-      <c r="S68">
+      <c r="R68">
         <v>5</v>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>CAMPBELL, 1967</t>
         </is>
@@ -3827,20 +3621,17 @@
         </is>
       </c>
       <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69">
         <v>60</v>
       </c>
-      <c r="J69">
+      <c r="I69">
         <v>5</v>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>VERHAART, 1970</t>
         </is>
       </c>
-      <c r="M69">
+      <c r="L69">
         <v>1.27</v>
       </c>
     </row>
@@ -3865,18 +3656,18 @@
           <t>as_printed</t>
         </is>
       </c>
-      <c r="G70">
+      <c r="F70">
         <v>5.3</v>
       </c>
-      <c r="M70">
+      <c r="L70">
         <v>0.37</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
         <is>
           <t>DOUGLAS and BARR, 1950</t>
         </is>
@@ -4163,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4FE2300-06AE-4850-A753-EF26EA22A95D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C7668F-DAD7-4D9D-A28A-72B8773F6941}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36704499-27A1-4F88-BB71-C753FE6C407A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B4CD45-8466-4915-8C9A-E4A1CCC3C4EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F038FE7E-C0EE-4F89-A2B6-125993CA7633}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DABD011-C6ED-4159-9ADC-AEE2D7B5F950}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3676,291 +3676,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C014377-6C98-4FAA-9941-DB008ECACDEE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A4D20D-9825-4288-9053-8DC8B2A7C207}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35CB4F1B-AC9F-4F92-9930-84548F76A068}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3676,4 +3676,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366806F6-D07C-4E92-9A86-EF1B2B2AF7C5}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0D97504-2A0D-49F6-99A9-61FFA53E9D6B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{079945FC-E81F-4726-89D8-2E606987E5E7}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366806F6-D07C-4E92-9A86-EF1B2B2AF7C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29DB3528-EC37-468A-9AC4-54316330161A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0D97504-2A0D-49F6-99A9-61FFA53E9D6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37F9D8E3-949B-4656-9F25-07A2B59D37E8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{079945FC-E81F-4726-89D8-2E606987E5E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94C38A05-45E8-4859-A6DB-F2BF03BB6B03}"/>
 </file>